--- a/vlearn-app/public/quiz_excel/Day_07_Data Foundations, Embedding _ Vector Store/Day_07_Phan_02_21_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_07_Data Foundations, Embedding _ Vector Store/Day_07_Phan_02_21_Cau.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bình phương từng chênh lệch trước khi cộng.</t>
+          <t>Khoảng cách Euclidean giữa a = [1, 2, 3] và b = [4, 2, -1]: d(a, b) = √((4 - 1)² + (2 - 2)² + (-1 - 3)²) = √(3² + 0² + (-4)²) = √(9 + 0 + 16) = √25 = 5.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cùng số chiều chưa chắc cùng không gian đã học.</t>
+          <t>Khi chuyển đổi hoặc thay đổi mô hình embeddings hay metric truy vấn, hai mô hình khác nhau có không gian vector hoàn toàn khác nhau (ngay cả khi cùng số chiều). Do đó, bắt buộc phải xác nhận metric, phương pháp chuẩn hóa và mô hình trên cả kho tài liệu lẫn truy vấn; nếu đổi mô hình phải re-embed toàn bộ kho và lập lại chỉ mục.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -888,7 +888,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Vector giống chiều không có nghĩa cùng hệ tọa độ.</t>
+          <t>Khi thay đổi mô hình embeddings cho một kho tài liệu đã chỉ mục, không thể tìm kiếm truy vấn của mô hình mới trên vector cũ vì khác không gian biểu diễn. Bắt buộc phải re-embed toàn bộ kho tài liệu và xây dựng chỉ mục tương thích trước khi chuyển đổi phục vụ.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1208,7 +1208,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Match ở tài liệu danh tính, không ở chunk ID duy nhất.</t>
+          <t>Trong thiết kế API quản lý vòng đời tài liệu, `delete_document(doc_id)` xóa toàn bộ các chunk thuộc về `doc_id` đó. Với `doc_id='A'`, lần gọi đầu tiên xóa toàn bộ 3 chunk A::0, A::1, A::2 và giữ lại B::0 (trả về 3); lần gọi thứ hai tài liệu A đã không còn nên trả về 0 mà không làm thay đổi kho hay báo lỗi bắt buộc.</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1256,7 +1256,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ một biến thay đổi và xác định rõ hành vi khi không có kết quả.</t>
+          <t>Khi cân chỉnh ngưỡng tương đồng (threshold), tăng ngưỡng làm tăng tỷ lệ rỗng (no-result) trong khi giảm ngưỡng làm tăng nhiễu. Quyết định đúng là đánh giá sự đánh đổi giữa recall và hậu quả của việc không có kết quả, từ đó chọn ngưỡng cân bằng kèm cơ chế fallback minh bạch.</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1471,7 +1471,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Citation không thể thay một thông tin thực không có trong ngữ cảnh.</t>
+          <t>Khi ngữ cảnh được truy xuất (retrieved context) không chứa thông tin trả lời cho câu hỏi của người dùng, hành vi tuân thủ nguyên tắc có căn cứ (groundedness) là tuyên bố rõ ràng không đủ thông tin hoặc yêu cầu người dùng làm rõ; không được bịa citation hay dùng kiến thức ngoài lề rồi gán nhãn trích dẫn giả mạo.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1577,7 +1577,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một filter chỉ hữu ích nếu field phân biệt ứng viên phù hợp.</t>
+          <t>Nếu bộ lọc (filter) theo thuộc tính `department` không làm thay đổi kết quả nào trên 20 truy vấn kiểm thử do toàn bộ các bản ghi trong kho đều có cùng giá trị department, trường này không mang lại giá trị phân loại (discriminatory utility) trong tập dữ liệu; nhóm cần xem xét loại bỏ hoặc thiết kế lại cấu trúc metadata.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1625,7 +1625,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Muốn locate cause phải giữ các layer khác cố định.</t>
+          <t>Khi nhóm thay đổi đồng thời nhiều thành phần (corpus, chunk size, embedding model, top-k, prompt) và điểm số tăng, nhóm không thể xác định thành phần nào là nguyên nhân chính gây ra cải thiện do hiện tượng đa biến (confounding variables). Bắt buộc phải thực hiện thử nghiệm cô lập từng biến trên tập benchmark đã đóng băng.</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>60</v>
@@ -1670,7 +1670,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dấu của chênh lệch mất đi sau bước bình phương.</t>
+          <t>Khoảng cách Euclidean giữa u = [-1, 2, 4] và v = [2, -2, 4]: d(u, v) = √((2 - (-1))² + (-2 - 2)² + (4 - 4)²) = √(3² + (-4)² + 0²) = √(9 + 16 + 0) = √25 = 5.</t>
         </is>
       </c>
     </row>
